--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Back_Summary.xlsx
@@ -413,28 +413,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="C1" t="inlineStr">
         <is>
-          <t>Distance 1</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Distance 2</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Angle</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Area</t>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -446,20 +451,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fiducial 1</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>121.26828</v>
+        <v>17.53752</v>
       </c>
       <c r="D2" t="n">
-        <v>86.24606</v>
+        <v>16.46642</v>
       </c>
       <c r="E2" t="n">
-        <v>92.30915</v>
+        <v>17.08957</v>
       </c>
       <c r="F2" t="n">
-        <v>529.04285</v>
+        <v>22.45243</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.19437</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +477,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>122.5985</v>
+        <v>17.1855</v>
       </c>
       <c r="D3" t="n">
-        <v>87.72253000000001</v>
+        <v>16.36902</v>
       </c>
       <c r="E3" t="n">
-        <v>94.39618</v>
+        <v>17.12713</v>
       </c>
       <c r="F3" t="n">
-        <v>533.13106</v>
+        <v>22.20108</v>
+      </c>
+      <c r="G3" t="n">
+        <v>34.4574</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +499,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>125.77282</v>
+        <v>17.12971</v>
       </c>
       <c r="D4" t="n">
-        <v>89.69635</v>
+        <v>16.46055</v>
       </c>
       <c r="E4" t="n">
-        <v>93.41201</v>
+        <v>16.86773</v>
       </c>
       <c r="F4" t="n">
-        <v>524.76153</v>
+        <v>22.41702</v>
+      </c>
+      <c r="G4" t="n">
+        <v>35.07343</v>
       </c>
     </row>
     <row r="5">
@@ -507,16 +521,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>123.14407</v>
+        <v>17.40021</v>
       </c>
       <c r="D5" t="n">
-        <v>88.00576</v>
+        <v>16.47172</v>
       </c>
       <c r="E5" t="n">
-        <v>92.30663</v>
+        <v>17.1888</v>
       </c>
       <c r="F5" t="n">
-        <v>526.2559</v>
+        <v>21.9668</v>
+      </c>
+      <c r="G5" t="n">
+        <v>34.16407</v>
       </c>
     </row>
     <row r="6">
@@ -526,16 +543,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>125.17221</v>
+        <v>17.4284</v>
       </c>
       <c r="D6" t="n">
-        <v>87.56187</v>
+        <v>16.46844</v>
       </c>
       <c r="E6" t="n">
-        <v>93.07285</v>
+        <v>17.00452</v>
       </c>
       <c r="F6" t="n">
-        <v>537.83293</v>
+        <v>22.07614</v>
+      </c>
+      <c r="G6" t="n">
+        <v>35.17945</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +565,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>121.92472</v>
+        <v>17.39153</v>
       </c>
       <c r="D7" t="n">
-        <v>88.22508000000001</v>
+        <v>16.47803</v>
       </c>
       <c r="E7" t="n">
-        <v>90.7234</v>
+        <v>16.81246</v>
       </c>
       <c r="F7" t="n">
-        <v>538.18213</v>
+        <v>22.15282</v>
+      </c>
+      <c r="G7" t="n">
+        <v>35.03395</v>
       </c>
     </row>
     <row r="8">
@@ -564,16 +587,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>124.50018</v>
+        <v>16.85862</v>
       </c>
       <c r="D8" t="n">
-        <v>87.12013</v>
+        <v>16.22076</v>
       </c>
       <c r="E8" t="n">
-        <v>92.62804</v>
+        <v>16.83552</v>
       </c>
       <c r="F8" t="n">
-        <v>529.96252</v>
+        <v>22.38942</v>
+      </c>
+      <c r="G8" t="n">
+        <v>35.22055</v>
       </c>
     </row>
     <row r="9">
@@ -583,16 +609,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>124.88566</v>
+        <v>17.19658</v>
       </c>
       <c r="D9" t="n">
-        <v>89.20985</v>
+        <v>16.58145</v>
       </c>
       <c r="E9" t="n">
-        <v>93.04286</v>
+        <v>17.15914</v>
       </c>
       <c r="F9" t="n">
-        <v>528.84521</v>
+        <v>22.01225</v>
+      </c>
+      <c r="G9" t="n">
+        <v>34.71504</v>
       </c>
     </row>
     <row r="10">
@@ -602,27 +631,50 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>124.26233</v>
+        <v>17.44616</v>
       </c>
       <c r="D10" t="n">
-        <v>88.78924000000001</v>
+        <v>16.35267</v>
       </c>
       <c r="E10" t="n">
-        <v>94.64225999999999</v>
+        <v>16.61602</v>
       </c>
       <c r="F10" t="n">
-        <v>533.28292</v>
+        <v>22.50867</v>
+      </c>
+      <c r="G10" t="n">
+        <v>34.96068</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Height</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Diameter</t>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -634,14 +686,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Micro Bump 3</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.711270000000001</v>
+        <v>17.39459</v>
       </c>
       <c r="D12" t="n">
-        <v>25.31204</v>
+        <v>17.1931</v>
+      </c>
+      <c r="E12" t="n">
+        <v>17.20052</v>
+      </c>
+      <c r="F12" t="n">
+        <v>44.15155</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05184</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.86018</v>
       </c>
     </row>
     <row r="13">
@@ -651,10 +715,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9.015599999999999</v>
+        <v>17.47007</v>
       </c>
       <c r="D13" t="n">
-        <v>24.67245</v>
+        <v>17.0085</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17.17281</v>
+      </c>
+      <c r="F13" t="n">
+        <v>43.63294</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05234</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.84497</v>
       </c>
     </row>
     <row r="14">
@@ -664,10 +740,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.88514</v>
+        <v>17.23388</v>
       </c>
       <c r="D14" t="n">
-        <v>25.33198</v>
+        <v>17.04769</v>
+      </c>
+      <c r="E14" t="n">
+        <v>17.05514</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42.99053</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05128</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.86579</v>
       </c>
     </row>
     <row r="15">
@@ -677,10 +765,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.953430000000001</v>
+        <v>17.58256</v>
       </c>
       <c r="D15" t="n">
-        <v>25.33371</v>
+        <v>17.20622</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.38012</v>
+      </c>
+      <c r="F15" t="n">
+        <v>44.23021</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.05211</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.91265</v>
       </c>
     </row>
     <row r="16">
@@ -690,10 +790,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.78562</v>
+        <v>17.46082</v>
       </c>
       <c r="D16" t="n">
-        <v>25.00185</v>
+        <v>16.8023</v>
+      </c>
+      <c r="E16" t="n">
+        <v>17.10024</v>
+      </c>
+      <c r="F16" t="n">
+        <v>43.14996</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05314</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.8723</v>
       </c>
     </row>
     <row r="17">
@@ -703,10 +815,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.84604</v>
+        <v>17.25023</v>
       </c>
       <c r="D17" t="n">
-        <v>25.14276</v>
+        <v>16.904</v>
+      </c>
+      <c r="E17" t="n">
+        <v>17.16267</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42.71291</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05221</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.84319</v>
       </c>
     </row>
     <row r="18">
@@ -716,10 +840,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.67104</v>
+        <v>17.34667</v>
       </c>
       <c r="D18" t="n">
-        <v>25.0853</v>
+        <v>16.74094</v>
+      </c>
+      <c r="E18" t="n">
+        <v>17.06856</v>
+      </c>
+      <c r="F18" t="n">
+        <v>44.49882</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05191</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.86017</v>
       </c>
     </row>
     <row r="19">
@@ -729,10 +865,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.842269999999999</v>
+        <v>17.52783</v>
       </c>
       <c r="D19" t="n">
-        <v>24.72578</v>
+        <v>17.0586</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17.07596</v>
+      </c>
+      <c r="F19" t="n">
+        <v>43.59259</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05121</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.81861</v>
       </c>
     </row>
     <row r="20">
@@ -742,272 +890,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.691380000000001</v>
+        <v>17.19947</v>
       </c>
       <c r="D20" t="n">
-        <v>24.98262</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>17.35302</v>
-      </c>
-      <c r="D22" t="n">
-        <v>17.18645</v>
-      </c>
-      <c r="E22" t="n">
-        <v>17.16733</v>
-      </c>
-      <c r="F22" t="n">
-        <v>44.20409</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.05211</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.85909</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>17.34053</v>
-      </c>
-      <c r="D23" t="n">
-        <v>17.01681</v>
-      </c>
-      <c r="E23" t="n">
-        <v>17.38415</v>
-      </c>
-      <c r="F23" t="n">
-        <v>43.6158</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.05143</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.88138</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>17.06883</v>
-      </c>
-      <c r="D24" t="n">
-        <v>17.02749</v>
-      </c>
-      <c r="E24" t="n">
-        <v>17.3248</v>
-      </c>
-      <c r="F24" t="n">
-        <v>42.90657</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.05147</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.85982</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>17.33649</v>
-      </c>
-      <c r="D25" t="n">
-        <v>17.28435</v>
-      </c>
-      <c r="E25" t="n">
-        <v>17.31189</v>
-      </c>
-      <c r="F25" t="n">
-        <v>43.81556</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.0518</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.85865</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>17.04663</v>
-      </c>
-      <c r="D26" t="n">
-        <v>17.08559</v>
-      </c>
-      <c r="E26" t="n">
-        <v>17.12456</v>
-      </c>
-      <c r="F26" t="n">
-        <v>43.63651</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.0524</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.89712</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>17.33645</v>
-      </c>
-      <c r="D27" t="n">
-        <v>16.92997</v>
-      </c>
-      <c r="E27" t="n">
-        <v>16.88996</v>
-      </c>
-      <c r="F27" t="n">
-        <v>44.25808</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.05225</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.89001</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>17.2604</v>
-      </c>
-      <c r="D28" t="n">
-        <v>17.0784</v>
-      </c>
-      <c r="E28" t="n">
-        <v>17.11395</v>
-      </c>
-      <c r="F28" t="n">
-        <v>44.03727</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.05095</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.84912</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>17.35569</v>
-      </c>
-      <c r="D29" t="n">
-        <v>17.17395</v>
-      </c>
-      <c r="E29" t="n">
-        <v>17.14031</v>
-      </c>
-      <c r="F29" t="n">
-        <v>44.21807</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.05183</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1.8717</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>17.3202</v>
-      </c>
-      <c r="D30" t="n">
-        <v>17.00393</v>
-      </c>
-      <c r="E30" t="n">
-        <v>17.11868</v>
-      </c>
-      <c r="F30" t="n">
-        <v>43.0926</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.05174</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.87941</v>
+        <v>16.98532</v>
+      </c>
+      <c r="E20" t="n">
+        <v>17.13811</v>
+      </c>
+      <c r="F20" t="n">
+        <v>44.21227</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05369</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.89437</v>
       </c>
     </row>
   </sheetData>
